--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>34134.83</v>
+        <v>34583.87</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>21844.69</v>
+        <v>22477.75</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>34219.61</v>
+        <v>34277.51</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7491.63</v>
+        <v>7492.49</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,68 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11520.54</v>
+        <v>11282.73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1093870-12-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>65.184.303-0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>KLEINROCK SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>36026.15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>542429-9-CM26</t>
+          <t>1093870-12-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SPIELUP SPA</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.582.047-2</t>
+          <t>77.146.212-K</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,128 +752,6 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7492.49</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2021-54-CM26</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>61.101.040-0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Estado Mayor Conjunto</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>TCHILECOM</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>11282.73</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1093870-12-CM26</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>65.184.303-0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>KLEINROCK SPA</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>77.146.212-K</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
         <v>36026.15</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
@@ -745,7 +745,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -759,6 +759,71 @@
         <v>36026.15</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1075963-13455-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>50944.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
